--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette entrée permet d’enregistrer une référence à un traitement dans un plan de traitement.</t>
+    <t>FrCarePlanDocument est un profil permettant d’enregistrer une référence à un traitement dans un plan de traitement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -656,8 +656,7 @@
 </t>
   </si>
   <si>
-    <t>Code de l’entrée.
- - Code indiquant que la référence est une ligne de traitement dans un plan de traitement</t>
+    <t>Code indiquant que la référence est une ligne de traitement dans un plan de traitement.</t>
   </si>
   <si>
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
